--- a/Backend/app/zavoz/exelfiles/файл_товары_9.xlsx
+++ b/Backend/app/zavoz/exelfiles/файл_товары_9.xlsx
@@ -1,20 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs code\Sofia_tech\Backend\app\zavoz\exelfiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7A46EE-903E-4962-9450-FD14D8678C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Товар Остатки" sheetId="2" r:id="rId1"/>
     <sheet name="Лист1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="75">
   <si>
     <t>DMD,кол-во</t>
   </si>
@@ -244,22 +256,24 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#\ ##0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -281,29 +295,29 @@
     </border>
     <border>
       <left style="thin">
-        <color/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="49" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -321,291 +335,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
     <a:clrScheme name="Стандартная">
       <a:dk1>
@@ -890,23 +621,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G67"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="2" width="12.88671875"/>
-    <col customWidth="1" min="2" max="3" style="2" width="16.88671875"/>
-    <col customWidth="1" min="4" max="4" style="2" width="65.44140625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" style="2" width="27"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" style="2" width="12.109375"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" style="2" width="19.33203125"/>
-    <col min="8" max="16384" style="2" width="8.88671875"/>
+    <col min="1" max="1" width="12.88671875" style="2" customWidth="1"/>
+    <col min="2" max="3" width="16.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="65.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="27" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>72</v>
       </c>
@@ -929,7 +662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -952,7 +685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -973,7 +706,7 @@
       </c>
       <c r="G3" s="4"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -994,7 +727,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1015,7 +748,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1036,7 +769,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1059,7 +792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1082,7 +815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1105,7 +838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1126,7 +859,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1147,7 +880,7 @@
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1170,7 +903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1191,7 +924,7 @@
       </c>
       <c r="G13" s="4"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1212,7 +945,7 @@
       </c>
       <c r="G14" s="4"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1233,7 +966,7 @@
       </c>
       <c r="G15" s="4"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1254,7 +987,7 @@
       </c>
       <c r="G16" s="4"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1275,7 +1008,7 @@
       </c>
       <c r="G17" s="4"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1296,7 +1029,7 @@
       </c>
       <c r="G18" s="4"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1317,7 +1050,7 @@
       </c>
       <c r="G19" s="4"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1338,7 +1071,7 @@
       </c>
       <c r="G20" s="4"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1359,7 +1092,7 @@
       </c>
       <c r="G21" s="4"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1380,7 +1113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1401,7 +1134,7 @@
       </c>
       <c r="G23" s="4"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1422,7 +1155,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1443,7 +1176,7 @@
       </c>
       <c r="G25" s="4"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1464,7 +1197,7 @@
       </c>
       <c r="G26" s="4"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1485,7 +1218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1506,7 +1239,7 @@
       </c>
       <c r="G28" s="4"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1527,7 +1260,7 @@
       </c>
       <c r="G29" s="4"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1548,7 +1281,7 @@
       </c>
       <c r="G30" s="4"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1571,7 +1304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1592,7 +1325,7 @@
       </c>
       <c r="G32" s="4"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1615,7 +1348,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1638,7 +1371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1659,7 +1392,7 @@
       </c>
       <c r="G35" s="4"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1680,7 +1413,7 @@
       </c>
       <c r="G36" s="4"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1703,7 +1436,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1724,7 +1457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1745,12 +1478,12 @@
       </c>
       <c r="G39" s="4"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C40" s="2">
         <v>9</v>
@@ -1766,12 +1499,12 @@
       </c>
       <c r="G40" s="4"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C41" s="2">
         <v>9</v>
@@ -1787,12 +1520,12 @@
       </c>
       <c r="G41" s="4"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C42" s="2">
         <v>9</v>
@@ -1808,12 +1541,12 @@
       </c>
       <c r="G42" s="4"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C43" s="2">
         <v>9</v>
@@ -1829,12 +1562,12 @@
       </c>
       <c r="G43" s="4"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C44" s="2">
         <v>9</v>
@@ -1850,12 +1583,12 @@
       </c>
       <c r="G44" s="4"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C45" s="2">
         <v>9</v>
@@ -1871,12 +1604,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C46" s="2">
         <v>9</v>
@@ -1892,12 +1625,12 @@
       </c>
       <c r="G46" s="4"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C47" s="2">
         <v>9</v>
@@ -1915,12 +1648,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C48" s="2">
         <v>9</v>
@@ -1936,12 +1669,12 @@
       </c>
       <c r="G48" s="4"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C49" s="2">
         <v>9</v>
@@ -1957,12 +1690,12 @@
       </c>
       <c r="G49" s="4"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>14</v>
+        <v>291</v>
       </c>
       <c r="C50" s="2">
         <v>9</v>
@@ -1978,12 +1711,12 @@
       </c>
       <c r="G50" s="4"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>13</v>
+        <v>460</v>
       </c>
       <c r="C51" s="2">
         <v>9</v>
@@ -1999,7 +1732,7 @@
       </c>
       <c r="G51" s="4"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2020,7 +1753,7 @@
       </c>
       <c r="G52" s="4"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2041,7 +1774,7 @@
       </c>
       <c r="G53" s="4"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2062,12 +1795,12 @@
       </c>
       <c r="G54" s="4"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C55" s="2">
         <v>9</v>
@@ -2083,12 +1816,12 @@
       </c>
       <c r="G55" s="4"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C56" s="2">
         <v>9</v>
@@ -2104,12 +1837,12 @@
       </c>
       <c r="G56" s="4"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="C57" s="2">
         <v>9</v>
@@ -2125,7 +1858,7 @@
       </c>
       <c r="G57" s="4"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2148,7 +1881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2169,7 +1902,7 @@
       </c>
       <c r="G59" s="4"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2190,7 +1923,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2211,12 +1944,12 @@
       </c>
       <c r="G61" s="4"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="2">
-        <v>45</v>
+        <v>528</v>
       </c>
       <c r="C62" s="2">
         <v>9</v>
@@ -2232,12 +1965,12 @@
       </c>
       <c r="G62" s="4"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>62</v>
       </c>
       <c r="B63" s="2">
-        <v>45</v>
+        <v>528</v>
       </c>
       <c r="C63" s="2">
         <v>9</v>
@@ -2253,12 +1986,12 @@
       </c>
       <c r="G63" s="4"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>63</v>
       </c>
       <c r="B64" s="2">
-        <v>45</v>
+        <v>528</v>
       </c>
       <c r="C64" s="2">
         <v>9</v>
@@ -2274,7 +2007,7 @@
       </c>
       <c r="G64" s="4"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2295,7 +2028,7 @@
       </c>
       <c r="G65" s="4"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -2316,12 +2049,12 @@
       </c>
       <c r="G66" s="4"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>66</v>
       </c>
       <c r="B67" s="2">
-        <v>14</v>
+        <v>294</v>
       </c>
       <c r="C67" s="2">
         <v>9</v>
@@ -2338,7 +2071,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;BТовар Остатки&amp;B
@@ -2350,9 +2083,10 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>